--- a/datos/repositorio rebate.xlsx
+++ b/datos/repositorio rebate.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC5D5C9-42FB-4225-B6E4-452CB37750EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED162D01-BD9F-4670-9130-80CBA51CF5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{36860D2A-3DCA-4432-91C5-5F03AF2A02ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$56</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1635,6 +1638,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F56" xr:uid="{98B8C3B4-95BA-4695-A269-4C26532AF790}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos/repositorio rebate.xlsx
+++ b/datos/repositorio rebate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED162D01-BD9F-4670-9130-80CBA51CF5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468D1989-D551-4FA3-85CA-BAF7C109A96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{36860D2A-3DCA-4432-91C5-5F03AF2A02ED}"/>
   </bookViews>
@@ -554,7 +554,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -774,7 +774,7 @@
         <v>7</v>
       </c>
       <c r="F13" s="1">
-        <v>3.5000000000000003E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
